--- a/y11581/samples/recharge_records.xlsx
+++ b/y11581/samples/recharge_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
   <si>
     <t>member_id</t>
   </si>
@@ -43,6 +43,15 @@
     <t>operator</t>
   </si>
   <si>
+    <t>is_cross_store</t>
+  </si>
+  <si>
+    <t>is_revoked</t>
+  </si>
+  <si>
+    <t>business_date</t>
+  </si>
+  <si>
     <t>M001</t>
   </si>
   <si>
@@ -79,6 +88,15 @@
     <t>M012</t>
   </si>
   <si>
+    <t>M013</t>
+  </si>
+  <si>
+    <t>M014</t>
+  </si>
+  <si>
+    <t>M015</t>
+  </si>
+  <si>
     <t>会员1号</t>
   </si>
   <si>
@@ -121,6 +139,15 @@
     <t>无效时间</t>
   </si>
   <si>
+    <t>跨日记录</t>
+  </si>
+  <si>
+    <t>跨店消费会员</t>
+  </si>
+  <si>
+    <t>撤销交易会员</t>
+  </si>
+  <si>
     <t>S02</t>
   </si>
   <si>
@@ -142,43 +169,40 @@
     <t>支付宝</t>
   </si>
   <si>
+    <t>微信</t>
+  </si>
+  <si>
     <t>银行卡</t>
   </si>
   <si>
-    <t>微信</t>
-  </si>
-  <si>
     <t>现金</t>
   </si>
   <si>
-    <t>2024-01-08 19:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-09 09:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-14 10:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-29 11:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-13 19:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-21 13:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-20 14:00:00</t>
+    <t>2024-01-31 20:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-14 16:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-03 20:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-22 21:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-06 14:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-13 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-05 14:00:00</t>
   </si>
   <si>
     <t>2024-01-11 17:00:00</t>
   </si>
   <si>
-    <t>2024-01-19 14:00:00</t>
-  </si>
-  <si>
-    <t>2024-01-01 17:00:00</t>
+    <t>2024-01-16 16:00:00</t>
   </si>
   <si>
     <t>2024-01-15 10:30:00</t>
@@ -193,13 +217,25 @@
     <t>invalid_date</t>
   </si>
   <si>
+    <t>2024-01-31 23:55:00</t>
+  </si>
+  <si>
+    <t>2024-01-20 10:00:00</t>
+  </si>
+  <si>
+    <t>2024-01-25 15:30:00</t>
+  </si>
+  <si>
+    <t>营业员C</t>
+  </si>
+  <si>
+    <t>营业员B</t>
+  </si>
+  <si>
     <t>营业员A</t>
   </si>
   <si>
-    <t>营业员B</t>
-  </si>
-  <si>
-    <t>营业员C</t>
+    <t>2024-02-01</t>
   </si>
 </sst>
 </file>
@@ -557,10 +593,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,306 +624,375 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2">
+        <v>362</v>
+      </c>
+      <c r="F2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>321</v>
+      </c>
+      <c r="F3">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>207</v>
+      </c>
+      <c r="F4">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5">
+        <v>427</v>
+      </c>
+      <c r="F5">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6">
+        <v>453</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>136</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>660</v>
+      </c>
+      <c r="F8">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>446</v>
+      </c>
+      <c r="F9">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>475</v>
+      </c>
+      <c r="F10">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2">
-        <v>633</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3">
-        <v>262</v>
-      </c>
-      <c r="F3">
-        <v>64</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11">
+        <v>710</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="I3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>734</v>
-      </c>
-      <c r="F4">
-        <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5">
-        <v>239</v>
-      </c>
-      <c r="F5">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6">
-        <v>173</v>
-      </c>
-      <c r="F6">
-        <v>55</v>
-      </c>
-      <c r="G6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="D12" t="s">
         <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>688</v>
-      </c>
-      <c r="F7">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8">
-        <v>891</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>238</v>
-      </c>
-      <c r="F9">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>824</v>
-      </c>
-      <c r="F10">
-        <v>21</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11">
-        <v>753</v>
-      </c>
-      <c r="F11">
-        <v>23</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -896,27 +1001,33 @@
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>72</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -925,27 +1036,33 @@
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>-100</v>
@@ -954,27 +1071,33 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>200</v>
@@ -983,13 +1106,127 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16">
+        <v>800</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17">
+        <v>1000</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
         <v>43</v>
       </c>
-      <c r="H15" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" t="s">
-        <v>59</v>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18">
+        <v>500</v>
+      </c>
+      <c r="F18">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
